--- a/development/backend/src/main/resources/templates/excel/matching-template.xlsx
+++ b/development/backend/src/main/resources/templates/excel/matching-template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="차량-라이더 매칭" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="차량-라이더 매칭" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -615,7 +615,8 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>서비스 유형 *</t>
+          <t>용도
+(자동 표시 — 수정 불가)</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">

--- a/development/backend/src/main/resources/templates/excel/matching-template.xlsx
+++ b/development/backend/src/main/resources/templates/excel/matching-template.xlsx
@@ -631,14 +631,14 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>계약형태 *
-(구독/렌탈)</t>
+          <t>계약형태
+(구독/렌탈 — 배송 전용)</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>인수방식 *
-(인수형/반납형)</t>
+          <t>계약 형태 *
+(배송: 인수형/반납형 · 클리닝: 직영/협력)</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
